--- a/docs/kanji_n2.xlsx
+++ b/docs/kanji_n2.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IG24-253\Documents\Work\ubuntu_practice\java\spring_boot\khans_kanji_english_practice\public\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ubuntu_practice\java\spring_boot\khans_kanji_english_practice\public\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683A6454-B477-41C4-BAC6-A64FF26CE403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="20" windowWidth="16100" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="125">
   <si>
     <t>Kanji</t>
   </si>
@@ -317,16 +318,142 @@
     <t>n2_evaluate.png</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>お祈り</t>
+  </si>
+  <si>
+    <t>技術</t>
+  </si>
+  <si>
+    <t>食品</t>
+  </si>
+  <si>
+    <t>健康</t>
+  </si>
+  <si>
+    <t>重量挙げ</t>
+  </si>
+  <si>
+    <t>信仰</t>
+  </si>
+  <si>
+    <t>規律</t>
+  </si>
+  <si>
+    <t>孤独</t>
+  </si>
+  <si>
+    <t>精神</t>
+  </si>
+  <si>
+    <t>物語</t>
+  </si>
+  <si>
+    <t>挑戦</t>
+  </si>
+  <si>
+    <t>創造</t>
+  </si>
+  <si>
+    <t>復活</t>
+  </si>
+  <si>
+    <t>自由</t>
+  </si>
+  <si>
+    <t>おいのり</t>
+  </si>
+  <si>
+    <t>ぎじゅつ</t>
+  </si>
+  <si>
+    <t>しょくひん</t>
+  </si>
+  <si>
+    <t>けんこう</t>
+  </si>
+  <si>
+    <t>じゅうりょうあげ</t>
+  </si>
+  <si>
+    <t>しんこう</t>
+  </si>
+  <si>
+    <t>きりつ</t>
+  </si>
+  <si>
+    <t>こどく</t>
+  </si>
+  <si>
+    <t>せいしん</t>
+  </si>
+  <si>
+    <t>ものがたり</t>
+  </si>
+  <si>
+    <t>ちょうせん</t>
+  </si>
+  <si>
+    <t>そうぞう</t>
+  </si>
+  <si>
+    <t>ふっかつ</t>
+  </si>
+  <si>
+    <t>じゆう</t>
+  </si>
+  <si>
+    <t>prayer</t>
+  </si>
+  <si>
+    <t>technology/technique</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>health</t>
+  </si>
+  <si>
+    <t>weightlifting</t>
+  </si>
+  <si>
+    <t>faith</t>
+  </si>
+  <si>
+    <t>discipline</t>
+  </si>
+  <si>
+    <t>solitude</t>
+  </si>
+  <si>
+    <t>spirit/mind</t>
+  </si>
+  <si>
+    <t>story</t>
+  </si>
+  <si>
+    <t>challenge</t>
+  </si>
+  <si>
+    <t>creation/creativity</t>
+  </si>
+  <si>
+    <t>rebirth</t>
+  </si>
+  <si>
+    <t>freedom</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -334,13 +461,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -388,7 +515,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -404,9 +531,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -444,9 +571,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -481,7 +608,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -516,7 +643,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -689,11 +816,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -707,7 +834,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -721,7 +848,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -735,7 +862,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -749,7 +876,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -763,7 +890,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -777,7 +904,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -791,7 +918,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -805,7 +932,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -819,7 +946,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -833,7 +960,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -847,7 +974,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -861,7 +988,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -875,7 +1002,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>61</v>
       </c>
@@ -889,7 +1016,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -903,7 +1030,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -917,7 +1044,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -931,7 +1058,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -945,7 +1072,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -959,7 +1086,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>79</v>
       </c>
@@ -973,7 +1100,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>81</v>
       </c>
@@ -985,6 +1112,160 @@
       </c>
       <c r="D21" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/docs/kanji_n2.xlsx
+++ b/docs/kanji_n2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ubuntu_practice\java\spring_boot\khans_kanji_english_practice\public\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ubuntu_practice\java\spring_boot\khans_kanji_english_practice\public\docs\temp_kanjis_to_add\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683A6454-B477-41C4-BAC6-A64FF26CE403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6444C0-12B4-4F3C-9A18-21E530250C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="312">
   <si>
     <t>Kanji</t>
   </si>
@@ -443,6 +443,567 @@
   </si>
   <si>
     <t>freedom</t>
+  </si>
+  <si>
+    <t>看板</t>
+  </si>
+  <si>
+    <t>板</t>
+  </si>
+  <si>
+    <t>羽毛</t>
+  </si>
+  <si>
+    <t>羽</t>
+  </si>
+  <si>
+    <t>羽根</t>
+  </si>
+  <si>
+    <t>成人式</t>
+  </si>
+  <si>
+    <t>第一</t>
+  </si>
+  <si>
+    <t>総合病院</t>
+  </si>
+  <si>
+    <t>賛成</t>
+  </si>
+  <si>
+    <t>拾う</t>
+  </si>
+  <si>
+    <t>鋭い</t>
+  </si>
+  <si>
+    <t>鈍い</t>
+  </si>
+  <si>
+    <t>肯定</t>
+  </si>
+  <si>
+    <t>否定</t>
+  </si>
+  <si>
+    <t>不便</t>
+  </si>
+  <si>
+    <t>浮く</t>
+  </si>
+  <si>
+    <t>沈む</t>
+  </si>
+  <si>
+    <t>翌日</t>
+  </si>
+  <si>
+    <t>お気の毒に</t>
+  </si>
+  <si>
+    <t>涙目</t>
+  </si>
+  <si>
+    <t>腹痛</t>
+  </si>
+  <si>
+    <t>腹</t>
+  </si>
+  <si>
+    <t>休息</t>
+  </si>
+  <si>
+    <t>血液</t>
+  </si>
+  <si>
+    <t>圧力</t>
+  </si>
+  <si>
+    <t>心臓</t>
+  </si>
+  <si>
+    <t>耳鼻科</t>
+  </si>
+  <si>
+    <t>鼻水</t>
+  </si>
+  <si>
+    <t>呼吸</t>
+  </si>
+  <si>
+    <t>吸う</t>
+  </si>
+  <si>
+    <t>食欲</t>
+  </si>
+  <si>
+    <t>欲しい</t>
+  </si>
+  <si>
+    <t>胃腸</t>
+  </si>
+  <si>
+    <t>泥棒</t>
+  </si>
+  <si>
+    <t>枯れる</t>
+  </si>
+  <si>
+    <t>溶岩</t>
+  </si>
+  <si>
+    <t>岩</t>
+  </si>
+  <si>
+    <t>涼しい</t>
+  </si>
+  <si>
+    <t>散歩</t>
+  </si>
+  <si>
+    <t>吹く</t>
+  </si>
+  <si>
+    <t>家畜</t>
+  </si>
+  <si>
+    <t>珍しい</t>
+  </si>
+  <si>
+    <t>氷</t>
+  </si>
+  <si>
+    <t>夫妻</t>
+  </si>
+  <si>
+    <t>挟む</t>
+  </si>
+  <si>
+    <t>漁船</t>
+  </si>
+  <si>
+    <t>漁師</t>
+  </si>
+  <si>
+    <t>海底</t>
+  </si>
+  <si>
+    <t>炭鉱</t>
+  </si>
+  <si>
+    <t>規則</t>
+  </si>
+  <si>
+    <t>測定</t>
+  </si>
+  <si>
+    <t>測る</t>
+  </si>
+  <si>
+    <t>授業</t>
+  </si>
+  <si>
+    <t>零下</t>
+  </si>
+  <si>
+    <t>上昇</t>
+  </si>
+  <si>
+    <t>昇る</t>
+  </si>
+  <si>
+    <t>大幅な</t>
+  </si>
+  <si>
+    <t>占める</t>
+  </si>
+  <si>
+    <t>占う</t>
+  </si>
+  <si>
+    <t>比較的</t>
+  </si>
+  <si>
+    <t>平年並み</t>
+  </si>
+  <si>
+    <t>かんばん</t>
+  </si>
+  <si>
+    <t>いた</t>
+  </si>
+  <si>
+    <t>うもう</t>
+  </si>
+  <si>
+    <t>はね</t>
+  </si>
+  <si>
+    <t>せいじんしき</t>
+  </si>
+  <si>
+    <t>だいいち</t>
+  </si>
+  <si>
+    <t>そうごうびょういん</t>
+  </si>
+  <si>
+    <t>さんせい</t>
+  </si>
+  <si>
+    <t>ひろう</t>
+  </si>
+  <si>
+    <t>するどい</t>
+  </si>
+  <si>
+    <t>にぶい</t>
+  </si>
+  <si>
+    <t>こうてい</t>
+  </si>
+  <si>
+    <t>ひてい</t>
+  </si>
+  <si>
+    <t>ふべん</t>
+  </si>
+  <si>
+    <t>うく</t>
+  </si>
+  <si>
+    <t>しずむ</t>
+  </si>
+  <si>
+    <t>よくじつ</t>
+  </si>
+  <si>
+    <t>おきのどくに</t>
+  </si>
+  <si>
+    <t>なみだめ</t>
+  </si>
+  <si>
+    <t>ふくつう</t>
+  </si>
+  <si>
+    <t>はら</t>
+  </si>
+  <si>
+    <t>きゅうそく</t>
+  </si>
+  <si>
+    <t>けつえき</t>
+  </si>
+  <si>
+    <t>あつりょく</t>
+  </si>
+  <si>
+    <t>しんぞう</t>
+  </si>
+  <si>
+    <t>じびか</t>
+  </si>
+  <si>
+    <t>はなみず</t>
+  </si>
+  <si>
+    <t>こきゅう</t>
+  </si>
+  <si>
+    <t>すう</t>
+  </si>
+  <si>
+    <t>しょくよく</t>
+  </si>
+  <si>
+    <t>ほしい</t>
+  </si>
+  <si>
+    <t>いちょう</t>
+  </si>
+  <si>
+    <t>どろぼう</t>
+  </si>
+  <si>
+    <t>かれる</t>
+  </si>
+  <si>
+    <t>ようがん</t>
+  </si>
+  <si>
+    <t>いわ</t>
+  </si>
+  <si>
+    <t>すずしい</t>
+  </si>
+  <si>
+    <t>さんぽ</t>
+  </si>
+  <si>
+    <t>ふく</t>
+  </si>
+  <si>
+    <t>かちく</t>
+  </si>
+  <si>
+    <t>めずらしい</t>
+  </si>
+  <si>
+    <t>こおり</t>
+  </si>
+  <si>
+    <t>ふさい</t>
+  </si>
+  <si>
+    <t>はさむ</t>
+  </si>
+  <si>
+    <t>ぎょせん</t>
+  </si>
+  <si>
+    <t>りょうし</t>
+  </si>
+  <si>
+    <t>かいてい</t>
+  </si>
+  <si>
+    <t>たんこう</t>
+  </si>
+  <si>
+    <t>きそく</t>
+  </si>
+  <si>
+    <t>そくてい</t>
+  </si>
+  <si>
+    <t>はかる</t>
+  </si>
+  <si>
+    <t>じゅぎょう</t>
+  </si>
+  <si>
+    <t>れいか</t>
+  </si>
+  <si>
+    <t>じょうしょう</t>
+  </si>
+  <si>
+    <t>のぼる</t>
+  </si>
+  <si>
+    <t>おおはばな</t>
+  </si>
+  <si>
+    <t>しめる</t>
+  </si>
+  <si>
+    <t>うらなう</t>
+  </si>
+  <si>
+    <t>ひかくてき</t>
+  </si>
+  <si>
+    <t>へいねんなみ</t>
+  </si>
+  <si>
+    <t>signboard</t>
+  </si>
+  <si>
+    <t>board</t>
+  </si>
+  <si>
+    <t>feather down</t>
+  </si>
+  <si>
+    <t>feather</t>
+  </si>
+  <si>
+    <t>feather wing</t>
+  </si>
+  <si>
+    <t>coming of age ceremony</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>general hospital</t>
+  </si>
+  <si>
+    <t>agreement</t>
+  </si>
+  <si>
+    <t>pick up</t>
+  </si>
+  <si>
+    <t>sharp</t>
+  </si>
+  <si>
+    <t>dull</t>
+  </si>
+  <si>
+    <t>affirmation</t>
+  </si>
+  <si>
+    <t>negation</t>
+  </si>
+  <si>
+    <t>inconvenient</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>sink</t>
+  </si>
+  <si>
+    <t>following day</t>
+  </si>
+  <si>
+    <t>my condolences</t>
+  </si>
+  <si>
+    <t>tearful eyes</t>
+  </si>
+  <si>
+    <t>stomachache</t>
+  </si>
+  <si>
+    <t>stomach</t>
+  </si>
+  <si>
+    <t>rest</t>
+  </si>
+  <si>
+    <t>blood</t>
+  </si>
+  <si>
+    <t>heart</t>
+  </si>
+  <si>
+    <t>ENT department</t>
+  </si>
+  <si>
+    <t>runny nose</t>
+  </si>
+  <si>
+    <t>breathing</t>
+  </si>
+  <si>
+    <t>inhale</t>
+  </si>
+  <si>
+    <t>appetite</t>
+  </si>
+  <si>
+    <t>want</t>
+  </si>
+  <si>
+    <t>stomach and intestines</t>
+  </si>
+  <si>
+    <t>thief</t>
+  </si>
+  <si>
+    <t>wither</t>
+  </si>
+  <si>
+    <t>lava</t>
+  </si>
+  <si>
+    <t>rock</t>
+  </si>
+  <si>
+    <t>cool</t>
+  </si>
+  <si>
+    <t>walk</t>
+  </si>
+  <si>
+    <t>blow</t>
+  </si>
+  <si>
+    <t>livestock</t>
+  </si>
+  <si>
+    <t>rare</t>
+  </si>
+  <si>
+    <t>ice</t>
+  </si>
+  <si>
+    <t>married couple</t>
+  </si>
+  <si>
+    <t>insert between</t>
+  </si>
+  <si>
+    <t>fishing boat</t>
+  </si>
+  <si>
+    <t>fisherman</t>
+  </si>
+  <si>
+    <t>sea bottom</t>
+  </si>
+  <si>
+    <t>coal mine</t>
+  </si>
+  <si>
+    <t>rule</t>
+  </si>
+  <si>
+    <t>measurement</t>
+  </si>
+  <si>
+    <t>measure</t>
+  </si>
+  <si>
+    <t>lesson</t>
+  </si>
+  <si>
+    <t>below zero</t>
+  </si>
+  <si>
+    <t>rise</t>
+  </si>
+  <si>
+    <t>rise climb</t>
+  </si>
+  <si>
+    <t>large scale</t>
+  </si>
+  <si>
+    <t>occupy</t>
+  </si>
+  <si>
+    <t>tell fortunes</t>
+  </si>
+  <si>
+    <t>relatively</t>
+  </si>
+  <si>
+    <t>average level</t>
+  </si>
+  <si>
+    <t>比べる</t>
+  </si>
+  <si>
+    <t>くらべる</t>
+  </si>
+  <si>
+    <t>compare</t>
+  </si>
+  <si>
+    <t>海の底</t>
+  </si>
+  <si>
+    <t>うみのそこ</t>
+  </si>
+  <si>
+    <t>bottom of the sea</t>
   </si>
 </sst>
 </file>
@@ -817,7 +1378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1266,6 +1827,699 @@
       </c>
       <c r="C35" t="s">
         <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>125</v>
+      </c>
+      <c r="B36" t="s">
+        <v>186</v>
+      </c>
+      <c r="C36" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" t="s">
+        <v>187</v>
+      </c>
+      <c r="C37" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" t="s">
+        <v>188</v>
+      </c>
+      <c r="C38" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" t="s">
+        <v>189</v>
+      </c>
+      <c r="C39" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" t="s">
+        <v>189</v>
+      </c>
+      <c r="C40" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>130</v>
+      </c>
+      <c r="B41" t="s">
+        <v>190</v>
+      </c>
+      <c r="C41" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" t="s">
+        <v>191</v>
+      </c>
+      <c r="C42" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>132</v>
+      </c>
+      <c r="B43" t="s">
+        <v>192</v>
+      </c>
+      <c r="C43" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" t="s">
+        <v>193</v>
+      </c>
+      <c r="C44" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" t="s">
+        <v>194</v>
+      </c>
+      <c r="C45" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" t="s">
+        <v>195</v>
+      </c>
+      <c r="C46" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C47" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>137</v>
+      </c>
+      <c r="B48" t="s">
+        <v>197</v>
+      </c>
+      <c r="C48" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>138</v>
+      </c>
+      <c r="B49" t="s">
+        <v>198</v>
+      </c>
+      <c r="C49" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" t="s">
+        <v>199</v>
+      </c>
+      <c r="C50" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" t="s">
+        <v>200</v>
+      </c>
+      <c r="C51" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>141</v>
+      </c>
+      <c r="B52" t="s">
+        <v>201</v>
+      </c>
+      <c r="C52" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>142</v>
+      </c>
+      <c r="B53" t="s">
+        <v>202</v>
+      </c>
+      <c r="C53" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>143</v>
+      </c>
+      <c r="B54" t="s">
+        <v>203</v>
+      </c>
+      <c r="C54" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" t="s">
+        <v>204</v>
+      </c>
+      <c r="C55" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>145</v>
+      </c>
+      <c r="B56" t="s">
+        <v>205</v>
+      </c>
+      <c r="C56" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>146</v>
+      </c>
+      <c r="B57" t="s">
+        <v>206</v>
+      </c>
+      <c r="C57" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>147</v>
+      </c>
+      <c r="B58" t="s">
+        <v>207</v>
+      </c>
+      <c r="C58" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>148</v>
+      </c>
+      <c r="B59" t="s">
+        <v>208</v>
+      </c>
+      <c r="C59" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60" t="s">
+        <v>209</v>
+      </c>
+      <c r="C60" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>150</v>
+      </c>
+      <c r="B61" t="s">
+        <v>210</v>
+      </c>
+      <c r="C61" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>151</v>
+      </c>
+      <c r="B62" t="s">
+        <v>211</v>
+      </c>
+      <c r="C62" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>152</v>
+      </c>
+      <c r="B63" t="s">
+        <v>212</v>
+      </c>
+      <c r="C63" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>153</v>
+      </c>
+      <c r="B64" t="s">
+        <v>213</v>
+      </c>
+      <c r="C64" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>154</v>
+      </c>
+      <c r="B65" t="s">
+        <v>214</v>
+      </c>
+      <c r="C65" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>155</v>
+      </c>
+      <c r="B66" t="s">
+        <v>215</v>
+      </c>
+      <c r="C66" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>156</v>
+      </c>
+      <c r="B67" t="s">
+        <v>216</v>
+      </c>
+      <c r="C67" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>157</v>
+      </c>
+      <c r="B68" t="s">
+        <v>217</v>
+      </c>
+      <c r="C68" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>158</v>
+      </c>
+      <c r="B69" t="s">
+        <v>218</v>
+      </c>
+      <c r="C69" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>159</v>
+      </c>
+      <c r="B70" t="s">
+        <v>219</v>
+      </c>
+      <c r="C70" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>160</v>
+      </c>
+      <c r="B71" t="s">
+        <v>220</v>
+      </c>
+      <c r="C71" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>161</v>
+      </c>
+      <c r="B72" t="s">
+        <v>221</v>
+      </c>
+      <c r="C72" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>162</v>
+      </c>
+      <c r="B73" t="s">
+        <v>222</v>
+      </c>
+      <c r="C73" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>163</v>
+      </c>
+      <c r="B74" t="s">
+        <v>223</v>
+      </c>
+      <c r="C74" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>164</v>
+      </c>
+      <c r="B75" t="s">
+        <v>224</v>
+      </c>
+      <c r="C75" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>165</v>
+      </c>
+      <c r="B76" t="s">
+        <v>225</v>
+      </c>
+      <c r="C76" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>166</v>
+      </c>
+      <c r="B77" t="s">
+        <v>226</v>
+      </c>
+      <c r="C77" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>167</v>
+      </c>
+      <c r="B78" t="s">
+        <v>227</v>
+      </c>
+      <c r="C78" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>168</v>
+      </c>
+      <c r="B79" t="s">
+        <v>228</v>
+      </c>
+      <c r="C79" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>169</v>
+      </c>
+      <c r="B80" t="s">
+        <v>229</v>
+      </c>
+      <c r="C80" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>170</v>
+      </c>
+      <c r="B81" t="s">
+        <v>230</v>
+      </c>
+      <c r="C81" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>171</v>
+      </c>
+      <c r="B82" t="s">
+        <v>231</v>
+      </c>
+      <c r="C82" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>172</v>
+      </c>
+      <c r="B83" t="s">
+        <v>232</v>
+      </c>
+      <c r="C83" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>173</v>
+      </c>
+      <c r="B84" t="s">
+        <v>233</v>
+      </c>
+      <c r="C84" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>174</v>
+      </c>
+      <c r="B85" t="s">
+        <v>234</v>
+      </c>
+      <c r="C85" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>175</v>
+      </c>
+      <c r="B86" t="s">
+        <v>235</v>
+      </c>
+      <c r="C86" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>176</v>
+      </c>
+      <c r="B87" t="s">
+        <v>236</v>
+      </c>
+      <c r="C87" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>177</v>
+      </c>
+      <c r="B88" t="s">
+        <v>237</v>
+      </c>
+      <c r="C88" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>178</v>
+      </c>
+      <c r="B89" t="s">
+        <v>238</v>
+      </c>
+      <c r="C89" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>179</v>
+      </c>
+      <c r="B90" t="s">
+        <v>239</v>
+      </c>
+      <c r="C90" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>180</v>
+      </c>
+      <c r="B91" t="s">
+        <v>240</v>
+      </c>
+      <c r="C91" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>181</v>
+      </c>
+      <c r="B92" t="s">
+        <v>241</v>
+      </c>
+      <c r="C92" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>182</v>
+      </c>
+      <c r="B93" t="s">
+        <v>242</v>
+      </c>
+      <c r="C93" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>183</v>
+      </c>
+      <c r="B94" t="s">
+        <v>243</v>
+      </c>
+      <c r="C94" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>184</v>
+      </c>
+      <c r="B95" t="s">
+        <v>244</v>
+      </c>
+      <c r="C95" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>185</v>
+      </c>
+      <c r="B96" t="s">
+        <v>245</v>
+      </c>
+      <c r="C96" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>306</v>
+      </c>
+      <c r="B97" t="s">
+        <v>307</v>
+      </c>
+      <c r="C97" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>309</v>
+      </c>
+      <c r="B98" t="s">
+        <v>310</v>
+      </c>
+      <c r="C98" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/docs/kanji_n2.xlsx
+++ b/docs/kanji_n2.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R911fa82d42e4431e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6bb1ad51c3c340d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -259,9 +259,6 @@
     <x:t xml:space="preserve">n2_evaluate.png</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">お祈り</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">おいのり</x:t>
   </x:si>
   <x:si>
@@ -463,27 +460,18 @@
     <x:t xml:space="preserve">agreement</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">拾う</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">ひろう</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">pick up</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">鋭い</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">するどい</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">sharp</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">鈍い</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">にぶい</x:t>
   </x:si>
   <x:si>
@@ -517,18 +505,12 @@
     <x:t xml:space="preserve">inconvenient</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">浮く</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">うく</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">float</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">沈む</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">しずむ</x:t>
   </x:si>
   <x:si>
@@ -640,9 +622,6 @@
     <x:t xml:space="preserve">breathing</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">吸う</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">すう</x:t>
   </x:si>
   <x:si>
@@ -658,9 +637,6 @@
     <x:t xml:space="preserve">appetite</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">欲しい</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">ほしい</x:t>
   </x:si>
   <x:si>
@@ -685,9 +661,6 @@
     <x:t xml:space="preserve">thief</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">枯れる</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">かれる</x:t>
   </x:si>
   <x:si>
@@ -712,9 +685,6 @@
     <x:t xml:space="preserve">rock</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">涼しい</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">すずしい</x:t>
   </x:si>
   <x:si>
@@ -730,9 +700,6 @@
     <x:t xml:space="preserve">walk</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">吹く</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">ふく</x:t>
   </x:si>
   <x:si>
@@ -748,9 +715,6 @@
     <x:t xml:space="preserve">livestock</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">珍しい</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">めずらしい</x:t>
   </x:si>
   <x:si>
@@ -775,9 +739,6 @@
     <x:t xml:space="preserve">married couple</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">挟む</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">はさむ</x:t>
   </x:si>
   <x:si>
@@ -838,9 +799,6 @@
     <x:t xml:space="preserve">measurement</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">測る</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">はかる</x:t>
   </x:si>
   <x:si>
@@ -874,9 +832,6 @@
     <x:t xml:space="preserve">rise</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">昇る</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">のぼる</x:t>
   </x:si>
   <x:si>
@@ -901,9 +856,6 @@
     <x:t xml:space="preserve">occupy</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">占う</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">うらなう</x:t>
   </x:si>
   <x:si>
@@ -926,9 +878,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">average level</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">比べる</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">くらべる</x:t>
@@ -1546,429 +1495,429 @@
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" t="s">
+      <x:c r="A22" t="str">
+        <x:v>祈</x:v>
+      </x:c>
+      <x:c r="B22" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B22" t="s">
+      <x:c r="C22" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="C22" t="s">
-        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B23" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B23" t="s">
+      <x:c r="C23" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="C23" t="s">
-        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B24" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B24" t="s">
+      <x:c r="C24" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="C24" t="s">
-        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B25" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B25" t="s">
+      <x:c r="C25" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="C25" t="s">
-        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B26" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="B26" t="s">
+      <x:c r="C26" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="C26" t="s">
-        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B27" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B27" t="s">
+      <x:c r="C27" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="C27" t="s">
-        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B28" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="B28" t="s">
+      <x:c r="C28" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="C28" t="s">
-        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B29" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="B29" t="s">
+      <x:c r="C29" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="C29" t="s">
-        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B30" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="B30" t="s">
+      <x:c r="C30" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="C30" t="s">
-        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B31" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="B31" t="s">
+      <x:c r="C31" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="C31" t="s">
-        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B32" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="B32" t="s">
+      <x:c r="C32" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="C32" t="s">
-        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B33" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="B33" t="s">
+      <x:c r="C33" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="C33" t="s">
-        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B34" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="B34" t="s">
+      <x:c r="C34" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="C34" t="s">
-        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B35" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="B35" t="s">
+      <x:c r="C35" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="C35" t="s">
-        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B36" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="B36" t="s">
+      <x:c r="C36" t="s">
         <x:v>126</x:v>
-      </x:c>
-      <x:c r="C36" t="s">
-        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B37" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B37" t="s">
+      <x:c r="C37" t="s">
         <x:v>129</x:v>
-      </x:c>
-      <x:c r="C37" t="s">
-        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B38" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="B38" t="s">
+      <x:c r="C38" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="C38" t="s">
-        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B39" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="B39" t="s">
+      <x:c r="C39" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="C39" t="s">
-        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B40" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C40" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="B40" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="C40" t="s">
-        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B41" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="B41" t="s">
+      <x:c r="C41" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="C41" t="s">
-        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B42" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="B42" t="s">
+      <x:c r="C42" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="C42" t="s">
-        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B43" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="B43" t="s">
+      <x:c r="C43" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="C43" t="s">
-        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B44" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="B44" t="s">
+      <x:c r="C44" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="C44" t="s">
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>拾</x:v>
+      </x:c>
+      <x:c r="B45" t="s">
         <x:v>150</x:v>
       </x:c>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" t="s">
+      <x:c r="C45" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="B45" t="s">
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>鋭</x:v>
+      </x:c>
+      <x:c r="B46" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="C45" t="s">
+      <x:c r="C46" t="s">
         <x:v>153</x:v>
       </x:c>
     </x:row>
-    <x:row r="46">
-      <x:c r="A46" t="s">
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>鈍</x:v>
+      </x:c>
+      <x:c r="B47" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="B46" t="s">
+      <x:c r="C47" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="C46" t="s">
-        <x:v>156</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="B47" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="C47" t="s">
-        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="s">
-        <x:v>160</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>161</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>162</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="s">
-        <x:v>163</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>164</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>165</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B50" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="C50" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>浮</x:v>
+      </x:c>
+      <x:c r="B51" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="C51" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="B50" t="s">
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>沈</x:v>
+      </x:c>
+      <x:c r="B52" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="C50" t="s">
+      <x:c r="C52" t="s">
         <x:v>168</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="B51" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="C51" t="s">
-        <x:v>171</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52">
-      <x:c r="A52" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="B52" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="C52" t="s">
-        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="s">
-        <x:v>175</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>176</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>177</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B54" t="s">
-        <x:v>179</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>180</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="s">
-        <x:v>181</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>182</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>183</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="s">
-        <x:v>184</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>185</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>186</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="s">
-        <x:v>187</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>188</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>189</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="s">
-        <x:v>190</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>191</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>192</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="s">
-        <x:v>193</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>194</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>195</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="s">
-        <x:v>196</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>197</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C60" t="s">
         <x:v>30</x:v>
@@ -1976,420 +1925,420 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="s">
-        <x:v>198</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>200</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="s">
-        <x:v>201</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>202</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>203</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="s">
-        <x:v>204</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>205</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>206</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="s">
-        <x:v>207</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>208</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>209</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" t="s">
-        <x:v>210</x:v>
+      <x:c r="A65" t="str">
+        <x:v>吸</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>211</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>212</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="s">
-        <x:v>213</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>214</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>215</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" t="s">
-        <x:v>216</x:v>
+      <x:c r="A67" t="str">
+        <x:v>欲</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>217</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>218</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="s">
-        <x:v>219</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>220</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>221</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="s">
-        <x:v>222</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>223</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>224</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" t="s">
-        <x:v>225</x:v>
+      <x:c r="A70" t="str">
+        <x:v>枯</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>226</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>227</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="s">
-        <x:v>228</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>229</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>230</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="s">
-        <x:v>231</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>232</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>233</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" t="s">
-        <x:v>234</x:v>
+      <x:c r="A73" t="str">
+        <x:v>涼</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>235</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C73" t="s">
-        <x:v>236</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="s">
-        <x:v>237</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>238</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C74" t="s">
-        <x:v>239</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" t="s">
-        <x:v>240</x:v>
+      <x:c r="A75" t="str">
+        <x:v>吹</x:v>
       </x:c>
       <x:c r="B75" t="s">
-        <x:v>241</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C75" t="s">
-        <x:v>242</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="s">
-        <x:v>243</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>244</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C76" t="s">
-        <x:v>245</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" t="s">
-        <x:v>246</x:v>
+      <x:c r="A77" t="str">
+        <x:v>珍</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>247</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C77" t="s">
-        <x:v>248</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="s">
-        <x:v>249</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>250</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C78" t="s">
-        <x:v>251</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="s">
-        <x:v>252</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>253</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>254</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" t="s">
-        <x:v>255</x:v>
+      <x:c r="A80" t="str">
+        <x:v>挟</x:v>
       </x:c>
       <x:c r="B80" t="s">
-        <x:v>256</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>257</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" t="s">
-        <x:v>258</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>259</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>260</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" t="s">
-        <x:v>261</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B82" t="s">
-        <x:v>262</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>263</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" t="s">
-        <x:v>264</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>265</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>266</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" t="s">
-        <x:v>267</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B84" t="s">
-        <x:v>268</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C84" t="s">
-        <x:v>269</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" t="s">
-        <x:v>270</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>271</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C85" t="s">
-        <x:v>272</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="s">
-        <x:v>273</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B86" t="s">
-        <x:v>274</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>275</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" t="s">
-        <x:v>276</x:v>
+      <x:c r="A87" t="str">
+        <x:v>測</x:v>
       </x:c>
       <x:c r="B87" t="s">
-        <x:v>277</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>278</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="s">
-        <x:v>279</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>280</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>281</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" t="s">
-        <x:v>282</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>283</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>284</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="s">
-        <x:v>285</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>286</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C90" t="s">
-        <x:v>287</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" t="s">
-        <x:v>288</x:v>
+      <x:c r="A91" t="str">
+        <x:v>昇</x:v>
       </x:c>
       <x:c r="B91" t="s">
-        <x:v>289</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C91" t="s">
-        <x:v>290</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" t="s">
-        <x:v>291</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>292</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C92" t="s">
-        <x:v>293</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" t="s">
-        <x:v>294</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B93" t="s">
-        <x:v>295</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C93" t="s">
-        <x:v>296</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" t="s">
-        <x:v>297</x:v>
+      <x:c r="A94" t="str">
+        <x:v>占</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>298</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C94" t="s">
-        <x:v>299</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" t="s">
-        <x:v>300</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B95" t="s">
-        <x:v>301</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C95" t="s">
-        <x:v>302</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" t="s">
-        <x:v>303</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>304</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C96" t="s">
-        <x:v>305</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" t="s">
-        <x:v>306</x:v>
+      <x:c r="A97" t="str">
+        <x:v>比</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>307</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>308</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" t="s">
-        <x:v>309</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>310</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C98" t="s">
-        <x:v>311</x:v>
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -2454,7 +2403,7 @@
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="4" t="str">
-        <x:v>補う</x:v>
+        <x:v>補</x:v>
       </x:c>
       <x:c r="B104" s="4" t="str">
         <x:v>おぎなう</x:v>
@@ -2502,7 +2451,7 @@
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="4" t="str">
-        <x:v>暴れる</x:v>
+        <x:v>暴</x:v>
       </x:c>
       <x:c r="B108" s="4" t="str">
         <x:v>あばれる</x:v>
@@ -2682,7 +2631,7 @@
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="4" t="str">
-        <x:v>競う</x:v>
+        <x:v>競</x:v>
       </x:c>
       <x:c r="B123" s="4" t="str">
         <x:v>きそう</x:v>
@@ -2706,7 +2655,7 @@
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="4" t="str">
-        <x:v>逆らう</x:v>
+        <x:v>逆</x:v>
       </x:c>
       <x:c r="B125" s="4" t="str">
         <x:v>さからう</x:v>
@@ -2730,7 +2679,7 @@
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="4" t="str">
-        <x:v>捜す</x:v>
+        <x:v>捜</x:v>
       </x:c>
       <x:c r="B127" s="4" t="str">
         <x:v>さがす</x:v>
@@ -2790,7 +2739,7 @@
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="4" t="str">
-        <x:v>叫ぶ</x:v>
+        <x:v>叫</x:v>
       </x:c>
       <x:c r="B132" s="4" t="str">
         <x:v>さけぶ</x:v>
@@ -2862,7 +2811,7 @@
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="4" t="str">
-        <x:v>雇う</x:v>
+        <x:v>雇</x:v>
       </x:c>
       <x:c r="B138" s="4" t="str">
         <x:v>やとう</x:v>
@@ -2898,7 +2847,7 @@
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="4" t="str">
-        <x:v>勢い</x:v>
+        <x:v>勢</x:v>
       </x:c>
       <x:c r="B141" s="4" t="str">
         <x:v>いきおい</x:v>
@@ -2910,7 +2859,7 @@
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="4" t="str">
-        <x:v>荒い</x:v>
+        <x:v>荒</x:v>
       </x:c>
       <x:c r="B142" s="4" t="str">
         <x:v>あらい</x:v>
@@ -2934,7 +2883,7 @@
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="4" t="str">
-        <x:v>耕す</x:v>
+        <x:v>耕</x:v>
       </x:c>
       <x:c r="B144" s="4" t="str">
         <x:v>たがやす</x:v>
@@ -2970,7 +2919,7 @@
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="4" t="str">
-        <x:v>賢い</x:v>
+        <x:v>賢</x:v>
       </x:c>
       <x:c r="B147" s="4" t="str">
         <x:v>かしこい</x:v>
@@ -2994,7 +2943,7 @@
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="4" t="str">
-        <x:v>勇ましい</x:v>
+        <x:v>勇</x:v>
       </x:c>
       <x:c r="B149" s="4" t="str">
         <x:v>いさましい</x:v>
@@ -3018,7 +2967,7 @@
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="4" t="str">
-        <x:v>敬う</x:v>
+        <x:v>敬</x:v>
       </x:c>
       <x:c r="B151" s="4" t="str">
         <x:v>うやまう</x:v>
@@ -3186,7 +3135,7 @@
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="4" t="str">
-        <x:v>導く</x:v>
+        <x:v>導</x:v>
       </x:c>
       <x:c r="B165" s="4" t="str">
         <x:v>みちびく</x:v>
@@ -3318,7 +3267,7 @@
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="4" t="str">
-        <x:v>干す</x:v>
+        <x:v>干</x:v>
       </x:c>
       <x:c r="B176" s="4" t="str">
         <x:v>ほす</x:v>
@@ -3474,7 +3423,7 @@
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="4" t="str">
-        <x:v>含む</x:v>
+        <x:v>含</x:v>
       </x:c>
       <x:c r="B189" s="4" t="str">
         <x:v>ふくむ</x:v>
@@ -3582,7 +3531,7 @@
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="4" t="str">
-        <x:v>述べる</x:v>
+        <x:v>述</x:v>
       </x:c>
       <x:c r="B198" s="4" t="str">
         <x:v>のべる</x:v>
@@ -3630,7 +3579,7 @@
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="4" t="str">
-        <x:v>採る</x:v>
+        <x:v>採</x:v>
       </x:c>
       <x:c r="B202" s="4" t="str">
         <x:v>とる</x:v>
@@ -3666,7 +3615,7 @@
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="4" t="str">
-        <x:v>濃い</x:v>
+        <x:v>濃</x:v>
       </x:c>
       <x:c r="B205" s="4" t="str">
         <x:v>こい</x:v>
@@ -3762,7 +3711,7 @@
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="4" t="str">
-        <x:v>乱れる</x:v>
+        <x:v>乱</x:v>
       </x:c>
       <x:c r="B213" s="4" t="str">
         <x:v>みだれる</x:v>
@@ -3834,7 +3783,7 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="4" t="str">
-        <x:v>曇り</x:v>
+        <x:v>曇</x:v>
       </x:c>
       <x:c r="B219" s="4" t="str">
         <x:v>くもり</x:v>
@@ -3882,7 +3831,7 @@
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="4" t="str">
-        <x:v>超す</x:v>
+        <x:v>超</x:v>
       </x:c>
       <x:c r="B223" s="4" t="str">
         <x:v>こす</x:v>
@@ -3942,7 +3891,7 @@
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="4" t="str">
-        <x:v>募る</x:v>
+        <x:v>募</x:v>
       </x:c>
       <x:c r="B228" s="4" t="str">
         <x:v>つのる</x:v>
@@ -4038,7 +3987,7 @@
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="4" t="str">
-        <x:v>固い</x:v>
+        <x:v>固</x:v>
       </x:c>
       <x:c r="B236" s="4" t="str">
         <x:v>かたい</x:v>
@@ -4098,7 +4047,7 @@
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="4" t="str">
-        <x:v>省く</x:v>
+        <x:v>省</x:v>
       </x:c>
       <x:c r="B241" s="4" t="str">
         <x:v>はぶく</x:v>
@@ -4122,7 +4071,7 @@
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="4" t="str">
-        <x:v>承る</x:v>
+        <x:v>承</x:v>
       </x:c>
       <x:c r="B243" s="4" t="str">
         <x:v>うけたまわる</x:v>
@@ -4206,7 +4155,7 @@
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="4" t="str">
-        <x:v>豊かな</x:v>
+        <x:v>豊</x:v>
       </x:c>
       <x:c r="B250" s="4" t="str">
         <x:v>ゆたかな</x:v>
@@ -4218,7 +4167,7 @@
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="4" t="str">
-        <x:v>泊まる</x:v>
+        <x:v>泊</x:v>
       </x:c>
       <x:c r="B251" s="4" t="str">
         <x:v>とまる</x:v>
@@ -4290,7 +4239,7 @@
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="4" t="str">
-        <x:v>辺り</x:v>
+        <x:v>辺</x:v>
       </x:c>
       <x:c r="B257" s="4" t="str">
         <x:v>あたり</x:v>
@@ -4770,7 +4719,7 @@
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="4" t="str">
-        <x:v>傾く</x:v>
+        <x:v>傾</x:v>
       </x:c>
       <x:c r="B297" s="4" t="str">
         <x:v>かたむく</x:v>
@@ -4878,7 +4827,7 @@
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="4" t="str">
-        <x:v>触れる</x:v>
+        <x:v>触</x:v>
       </x:c>
       <x:c r="B306" s="4" t="str">
         <x:v>ふれる</x:v>
@@ -4962,7 +4911,7 @@
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="4" t="str">
-        <x:v>柔らかい</x:v>
+        <x:v>柔</x:v>
       </x:c>
       <x:c r="B313" s="4" t="str">
         <x:v>やわらかい</x:v>
@@ -4986,7 +4935,7 @@
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="4" t="str">
-        <x:v>香り</x:v>
+        <x:v>香</x:v>
       </x:c>
       <x:c r="B315" s="4" t="str">
         <x:v>かおり</x:v>
@@ -4998,7 +4947,7 @@
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="4" t="str">
-        <x:v>軟らかい</x:v>
+        <x:v>軟</x:v>
       </x:c>
       <x:c r="B316" s="4" t="str">
         <x:v>やわらかい</x:v>
@@ -5010,7 +4959,7 @@
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="4" t="str">
-        <x:v>溶ける</x:v>
+        <x:v>溶</x:v>
       </x:c>
       <x:c r="B317" s="4" t="str">
         <x:v>とける</x:v>
@@ -5046,7 +4995,7 @@
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="4" t="str">
-        <x:v>塗る</x:v>
+        <x:v>塗</x:v>
       </x:c>
       <x:c r="B320" s="4" t="str">
         <x:v>ぬる</x:v>
@@ -5118,7 +5067,7 @@
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="4" t="str">
-        <x:v>乾く</x:v>
+        <x:v>乾</x:v>
       </x:c>
       <x:c r="B326" s="4" t="str">
         <x:v>かわく</x:v>
@@ -5214,7 +5163,7 @@
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="4" t="str">
-        <x:v>防ぐ</x:v>
+        <x:v>防</x:v>
       </x:c>
       <x:c r="B334" s="4" t="str">
         <x:v>ふせぐ</x:v>
@@ -5238,7 +5187,7 @@
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="4" t="str">
-        <x:v>悩む</x:v>
+        <x:v>悩</x:v>
       </x:c>
       <x:c r="B336" s="4" t="str">
         <x:v>なやむ</x:v>
@@ -5274,7 +5223,7 @@
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="4" t="str">
-        <x:v>刺す</x:v>
+        <x:v>刺</x:v>
       </x:c>
       <x:c r="B339" s="4" t="str">
         <x:v>さす</x:v>
@@ -5334,7 +5283,7 @@
     </x:row>
     <x:row r="344">
       <x:c r="A344" s="4" t="str">
-        <x:v>浴びる</x:v>
+        <x:v>浴</x:v>
       </x:c>
       <x:c r="B344" s="4" t="str">
         <x:v>あびる</x:v>
@@ -5406,7 +5355,7 @@
     </x:row>
     <x:row r="350">
       <x:c r="A350" s="4" t="str">
-        <x:v>造る</x:v>
+        <x:v>造</x:v>
       </x:c>
       <x:c r="B350" s="4" t="str">
         <x:v>つくる</x:v>
@@ -5454,7 +5403,7 @@
     </x:row>
     <x:row r="354">
       <x:c r="A354" s="4" t="str">
-        <x:v>沸く</x:v>
+        <x:v>沸</x:v>
       </x:c>
       <x:c r="B354" s="4" t="str">
         <x:v>わく</x:v>
@@ -5490,7 +5439,7 @@
     </x:row>
     <x:row r="357">
       <x:c r="A357" s="4" t="str">
-        <x:v>栄える</x:v>
+        <x:v>栄</x:v>
       </x:c>
       <x:c r="B357" s="4" t="str">
         <x:v>さかえる</x:v>
@@ -5610,7 +5559,7 @@
     </x:row>
     <x:row r="367">
       <x:c r="A367" s="4" t="str">
-        <x:v>お祝い</x:v>
+        <x:v>祝</x:v>
       </x:c>
       <x:c r="B367" s="4" t="str">
         <x:v>おいわい</x:v>
@@ -5658,7 +5607,7 @@
     </x:row>
     <x:row r="371">
       <x:c r="A371" s="4" t="str">
-        <x:v>伸びる</x:v>
+        <x:v>伸</x:v>
       </x:c>
       <x:c r="B371" s="4" t="str">
         <x:v>のびる</x:v>
@@ -5730,7 +5679,7 @@
     </x:row>
     <x:row r="377">
       <x:c r="A377" s="4" t="str">
-        <x:v>拝む</x:v>
+        <x:v>拝</x:v>
       </x:c>
       <x:c r="B377" s="4" t="str">
         <x:v>おがむ</x:v>
@@ -5742,7 +5691,7 @@
     </x:row>
     <x:row r="378">
       <x:c r="A378" s="4" t="str">
-        <x:v>伺う</x:v>
+        <x:v>伺</x:v>
       </x:c>
       <x:c r="B378" s="4" t="str">
         <x:v>うかがう</x:v>
@@ -5826,7 +5775,7 @@
     </x:row>
     <x:row r="385">
       <x:c r="A385" s="4" t="str">
-        <x:v>囲む</x:v>
+        <x:v>囲</x:v>
       </x:c>
       <x:c r="B385" s="4" t="str">
         <x:v>かこむ</x:v>
@@ -5934,7 +5883,7 @@
     </x:row>
     <x:row r="394">
       <x:c r="A394" s="4" t="str">
-        <x:v>憎い</x:v>
+        <x:v>憎</x:v>
       </x:c>
       <x:c r="B394" s="4" t="str">
         <x:v>にくい</x:v>
@@ -5982,7 +5931,7 @@
     </x:row>
     <x:row r="398">
       <x:c r="A398" s="4" t="str">
-        <x:v>細い</x:v>
+        <x:v>細</x:v>
       </x:c>
       <x:c r="B398" s="4" t="str">
         <x:v>ほそい</x:v>
@@ -6042,7 +5991,7 @@
     </x:row>
     <x:row r="403">
       <x:c r="A403" s="4" t="str">
-        <x:v>汚い</x:v>
+        <x:v>汚</x:v>
       </x:c>
       <x:c r="B403" s="4" t="str">
         <x:v>きたない</x:v>
@@ -6138,7 +6087,7 @@
     </x:row>
     <x:row r="411">
       <x:c r="A411" s="4" t="str">
-        <x:v>凍る</x:v>
+        <x:v>凍</x:v>
       </x:c>
       <x:c r="B411" s="4" t="str">
         <x:v>こおる</x:v>
@@ -6186,7 +6135,7 @@
     </x:row>
     <x:row r="415">
       <x:c r="A415" s="4" t="str">
-        <x:v>効く</x:v>
+        <x:v>効</x:v>
       </x:c>
       <x:c r="B415" s="4" t="str">
         <x:v>きく</x:v>
@@ -6246,7 +6195,7 @@
     </x:row>
     <x:row r="420">
       <x:c r="A420" s="4" t="str">
-        <x:v>燃える</x:v>
+        <x:v>燃</x:v>
       </x:c>
       <x:c r="B420" s="4" t="str">
         <x:v>もえる</x:v>
@@ -6354,7 +6303,7 @@
     </x:row>
     <x:row r="429">
       <x:c r="A429" s="4" t="str">
-        <x:v>震える</x:v>
+        <x:v>震</x:v>
       </x:c>
       <x:c r="B429" s="4" t="str">
         <x:v>ふるえる</x:v>
@@ -6378,7 +6327,7 @@
     </x:row>
     <x:row r="431">
       <x:c r="A431" s="4" t="str">
-        <x:v>延びる</x:v>
+        <x:v>延</x:v>
       </x:c>
       <x:c r="B431" s="4" t="str">
         <x:v>のびる</x:v>
@@ -6450,7 +6399,7 @@
     </x:row>
     <x:row r="437">
       <x:c r="A437" s="4" t="str">
-        <x:v>移る</x:v>
+        <x:v>移</x:v>
       </x:c>
       <x:c r="B437" s="4" t="str">
         <x:v>うつる</x:v>
@@ -6486,7 +6435,7 @@
     </x:row>
     <x:row r="440">
       <x:c r="A440" s="4" t="str">
-        <x:v>周り</x:v>
+        <x:v>周</x:v>
       </x:c>
       <x:c r="B440" s="4" t="str">
         <x:v>まわり</x:v>
@@ -6594,7 +6543,7 @@
     </x:row>
     <x:row r="449">
       <x:c r="A449" s="4" t="str">
-        <x:v>預ける</x:v>
+        <x:v>預</x:v>
       </x:c>
       <x:c r="B449" s="4" t="str">
         <x:v>あずける</x:v>
@@ -6618,7 +6567,7 @@
     </x:row>
     <x:row r="451">
       <x:c r="A451" s="4" t="str">
-        <x:v>照らす</x:v>
+        <x:v>照</x:v>
       </x:c>
       <x:c r="B451" s="4" t="str">
         <x:v>てらす</x:v>
@@ -6642,7 +6591,7 @@
     </x:row>
     <x:row r="453">
       <x:c r="A453" s="4" t="str">
-        <x:v>硬い</x:v>
+        <x:v>硬</x:v>
       </x:c>
       <x:c r="B453" s="4" t="str">
         <x:v>かたい</x:v>
@@ -6678,7 +6627,7 @@
     </x:row>
     <x:row r="456">
       <x:c r="A456" s="4" t="str">
-        <x:v>温かい</x:v>
+        <x:v>温</x:v>
       </x:c>
       <x:c r="B456" s="4" t="str">
         <x:v>あたたかい</x:v>
@@ -6798,7 +6747,7 @@
     </x:row>
     <x:row r="466">
       <x:c r="A466" s="4" t="str">
-        <x:v>幼い</x:v>
+        <x:v>幼</x:v>
       </x:c>
       <x:c r="B466" s="4" t="str">
         <x:v>おさない</x:v>
@@ -6894,7 +6843,7 @@
     </x:row>
     <x:row r="474">
       <x:c r="A474" s="4" t="str">
-        <x:v>湿る</x:v>
+        <x:v>湿</x:v>
       </x:c>
       <x:c r="B474" s="4" t="str">
         <x:v>しめる</x:v>
@@ -6966,7 +6915,7 @@
     </x:row>
     <x:row r="480">
       <x:c r="A480" s="4" t="str">
-        <x:v>量る</x:v>
+        <x:v>量</x:v>
       </x:c>
       <x:c r="B480" s="4" t="str">
         <x:v>はかる</x:v>
@@ -7122,7 +7071,7 @@
     </x:row>
     <x:row r="493">
       <x:c r="A493" s="4" t="str">
-        <x:v>捨てる</x:v>
+        <x:v>捨</x:v>
       </x:c>
       <x:c r="B493" s="4" t="str">
         <x:v>すてる</x:v>
@@ -7218,7 +7167,7 @@
     </x:row>
     <x:row r="501">
       <x:c r="A501" s="4" t="str">
-        <x:v>掃く</x:v>
+        <x:v>掃</x:v>
       </x:c>
       <x:c r="B501" s="4" t="str">
         <x:v>はく</x:v>
@@ -7278,7 +7227,7 @@
     </x:row>
     <x:row r="506">
       <x:c r="A506" s="4" t="str">
-        <x:v>改める</x:v>
+        <x:v>改</x:v>
       </x:c>
       <x:c r="B506" s="4" t="str">
         <x:v>あらためる</x:v>
@@ -7326,7 +7275,7 @@
     </x:row>
     <x:row r="510">
       <x:c r="A510" s="4" t="str">
-        <x:v>快い</x:v>
+        <x:v>快</x:v>
       </x:c>
       <x:c r="B510" s="4" t="str">
         <x:v>こころよい</x:v>
@@ -7386,7 +7335,7 @@
     </x:row>
     <x:row r="515">
       <x:c r="A515" s="4" t="str">
-        <x:v>包む</x:v>
+        <x:v>包</x:v>
       </x:c>
       <x:c r="B515" s="4" t="str">
         <x:v>つつむ</x:v>
@@ -7422,7 +7371,7 @@
     </x:row>
     <x:row r="518">
       <x:c r="A518" s="4" t="str">
-        <x:v>再び</x:v>
+        <x:v>再</x:v>
       </x:c>
       <x:c r="B518" s="4" t="str">
         <x:v>ふたたび</x:v>
